--- a/e2e/fixtures/assets-empty.xlsx
+++ b/e2e/fixtures/assets-empty.xlsx
@@ -20,6 +20,9 @@
   </si>
   <si>
     <t>Model</t>
+  </si>
+  <si>
+    <t>Brand</t>
   </si>
   <si>
     <t>Serial</t>
@@ -49,7 +52,16 @@
     <t>Warranty until</t>
   </si>
   <si>
+    <t>Loan until</t>
+  </si>
+  <si>
     <t>Vendor</t>
+  </si>
+  <si>
+    <t>Provenance</t>
+  </si>
+  <si>
+    <t>Invoice / receipt no.</t>
   </si>
   <si>
     <t>RMA ref</t>
@@ -104,18 +116,22 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="20" customWidth="1"/>
-    <col min="13" max="13" width="16" customWidth="1"/>
-    <col min="14" max="14" width="40" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="24" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -161,6 +177,18 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
 </worksheet>
